--- a/checklist_forms/036_gym_equipment_monthly_inspection_checklist_form--checklist_forms.xlsx
+++ b/checklist_forms/036_gym_equipment_monthly_inspection_checklist_form--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good', 'value': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'needs_attention',_'value':_'needs_attention'}</t>
+          <t>needs_attention</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Needs Attention', 'value': 'needs_attention'}</t>
+          <t>needs attention</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'defective',_'value':_'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Defective', 'value': 'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'good', 'value': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'needs_attention',_'value':_'needs_attention'}</t>
+          <t>needs_attention</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'needs_attention', 'value': 'needs_attention'}</t>
+          <t>needs attention</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'defective',_'value':_'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'defective', 'value': 'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'good', 'value': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'needs_attention',_'value':_'needs_attention'}</t>
+          <t>needs_attention</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'needs_attention', 'value': 'needs_attention'}</t>
+          <t>needs attention</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'defective',_'value':_'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'defective', 'value': 'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'good', 'value': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'needs_attention',_'value':_'needs_attention'}</t>
+          <t>needs_attention</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'needs_attention', 'value': 'needs_attention'}</t>
+          <t>needs attention</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'defective',_'value':_'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'defective', 'value': 'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'good', 'value': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'needs_attention',_'value':_'needs_attention'}</t>
+          <t>needs_attention</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'needs_attention', 'value': 'needs_attention'}</t>
+          <t>needs attention</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'defective',_'value':_'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'defective', 'value': 'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'good', 'value': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'needs_attention',_'value':_'needs_attention'}</t>
+          <t>needs_attention</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'needs_attention', 'value': 'needs_attention'}</t>
+          <t>needs attention</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'defective',_'value':_'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'defective', 'value': 'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'good', 'value': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'needs_attention',_'value':_'needs_attention'}</t>
+          <t>needs_attention</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'needs_attention', 'value': 'needs_attention'}</t>
+          <t>needs attention</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'defective',_'value':_'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'defective', 'value': 'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'good', 'value': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'needs_attention',_'value':_'needs_attention'}</t>
+          <t>needs_attention</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'needs_attention', 'value': 'needs_attention'}</t>
+          <t>needs attention</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'defective',_'value':_'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'defective', 'value': 'defective'}</t>
+          <t>defective</t>
         </is>
       </c>
     </row>
